--- a/photo_release_form_templates/013_photo_release_form_for_minors--photo_release_form_templates.xlsx
+++ b/photo_release_form_templates/013_photo_release_form_for_minors--photo_release_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,8 +869,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,12 +898,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'portrait',_'value':_'portrait'}</t>
+          <t>portrait</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Portrait', 'value': 'Portrait'}</t>
+          <t>Portrait</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'landscape',_'value':_'landscape'}</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Landscape', 'value': 'Landscape'}</t>
+          <t>Landscape</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'full',_'value':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Full', 'value': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'sibling',_'value':_'sibling'}</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Sibling', 'value': 'Sibling'}</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'public',_'value':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Public', 'value': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non-public',_'value':_'non-public'}</t>
+          <t>non-public</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Non-Public', 'value': 'Non-Public'}</t>
+          <t>Non-Public</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'retouch',_'value':_'retouch'}</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Retouch', 'value': 'Retouch'}</t>
+          <t>Retouch</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'do_not_retouch',_'value':_'do_not_retouch'}</t>
+          <t>do_not_retouch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Do Not Retouch', 'value': 'Do Not Retouch'}</t>
+          <t>Do Not Retouch</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'print',_'value':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Print', 'value': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'publish',_'value':_'publish'}</t>
+          <t>publish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Publish', 'value': 'Publish'}</t>
+          <t>Publish</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'share_on_facebook',_'value':_'share_on_facebook'}</t>
+          <t>share_on_facebook</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Share on Facebook', 'value': 'Share on Facebook'}</t>
+          <t>Share on Facebook</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'share_on_twitter',_'value':_'share_on_twitter'}</t>
+          <t>share_on_twitter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Share on Twitter', 'value': 'Share on Twitter'}</t>
+          <t>Share on Twitter</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'share_on_instagram',_'value':_'share_on_instagram'}</t>
+          <t>share_on_instagram</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Share on Instagram', 'value': 'Share on Instagram'}</t>
+          <t>Share on Instagram</t>
         </is>
       </c>
     </row>
